--- a/english/backup/traducciones.xlsx
+++ b/english/backup/traducciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\python\english\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84BF0119-85C2-42F1-9495-7FD70CDF7897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3582BD37-397F-4E1D-92B2-3B2FB5AED79B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,13 +23,14 @@
   </definedNames>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId4"/>
+    <pivotCache cacheId="1" r:id="rId4"/>
   </pivotCaches>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7713" uniqueCount="5015">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7717" uniqueCount="5018">
   <si>
     <t>word</t>
   </si>
@@ -15074,6 +15075,15 @@
   </si>
   <si>
     <t>gasped</t>
+  </si>
+  <si>
+    <t>evolving</t>
+  </si>
+  <si>
+    <t>graceful</t>
+  </si>
+  <si>
+    <t>squeaking</t>
   </si>
 </sst>
 </file>
@@ -36648,7 +36658,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{061658BE-3B1A-4888-8436-48FEB0493D88}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{061658BE-3B1A-4888-8436-48FEB0493D88}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:D35" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -86003,7 +86013,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6B3C0A2-850D-42EC-978A-945A59BF5661}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:C121"/>
+  <dimension ref="A1:C125"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" customWidth="1"/>
@@ -87031,6 +87041,26 @@
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>5014</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>5015</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>5016</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>5017</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>4332</v>
       </c>
     </row>
   </sheetData>
